--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,53 +417,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Actual Winner</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>market_prob_home_win</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>46159.83333333334</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -511,7 +499,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>46160.85416666666</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -547,7 +535,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>46161.83333333334</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -583,7 +571,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>46162.85416666666</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -609,8 +597,44 @@
           <t>42500312</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6843</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46163.83333333334</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>42500302</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -1,37 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="3">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,82 +66,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -203,6 +152,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -237,6 +187,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -271,20 +222,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -406,237 +353,239 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H7"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Home Team</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Away Team</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Predicted Winner</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>probability_home_win</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>gameId</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Actual Winner</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>market_prob_home_win</t>
-        </is>
+      <c r="A1" t="str">
+        <v>Date</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Home Team</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Away Team</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Predicted Winner</v>
+      </c>
+      <c r="E1" t="str">
+        <v>probability_home_win</v>
+      </c>
+      <c r="F1" t="str">
+        <v>gameId</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Actual Winner</v>
+      </c>
+      <c r="H1" t="str">
+        <v>market_prob_home_win</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46159.83333333334</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0.6375999999999999</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>42500207</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
+      <c r="A2" t="str">
+        <v>2026-05-17 20:00:00</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Detroit Pistons</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Cleveland Cavaliers</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Detroit Pistons</v>
+      </c>
+      <c r="E2" t="str">
+        <v>0.6376</v>
+      </c>
+      <c r="F2" t="str">
+        <v>42500207</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Cleveland Cavaliers</v>
+      </c>
+      <c r="H2" t="str">
         <v>0.6279</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>46160.85416666666</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+      <c r="A3" t="str">
+        <v>2026-05-18 20:30:00</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Oklahoma City Thunder</v>
+      </c>
+      <c r="C3" t="str">
+        <v>San Antonio Spurs</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Oklahoma City Thunder</v>
+      </c>
+      <c r="E3" t="str">
         <v>0.8002</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>42500311</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0.6778999999999999</v>
+      <c r="F3" t="str">
+        <v>42500311</v>
+      </c>
+      <c r="G3" t="str">
+        <v>San Antonio Spurs</v>
+      </c>
+      <c r="H3" t="str">
+        <v>0.6779</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46161.83333333334</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
+      <c r="A4" t="str">
+        <v>2026-05-19 20:00:00</v>
+      </c>
+      <c r="B4" t="str">
+        <v>New York Knicks</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Cleveland Cavaliers</v>
+      </c>
+      <c r="D4" t="str">
+        <v>New York Knicks</v>
+      </c>
+      <c r="E4" t="str">
         <v>0.837</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>42500301</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
+      <c r="F4" t="str">
+        <v>42500301</v>
+      </c>
+      <c r="G4" t="str">
+        <v>New York Knicks</v>
+      </c>
+      <c r="H4" t="str">
         <v>0.6841</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46162.85416666666</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0.6623931623931624</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>42500312</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
+      <c r="A5" t="str">
+        <v>2026-05-20 20:30:00</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Oklahoma City Thunder</v>
+      </c>
+      <c r="C5" t="str">
+        <v>San Antonio Spurs</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Oklahoma City Thunder</v>
+      </c>
+      <c r="E5" t="str">
+        <v>0.662393162</v>
+      </c>
+      <c r="F5" t="str">
+        <v>42500312</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Oklahoma City Thunder</v>
+      </c>
+      <c r="H5" t="str">
         <v>0.6843</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46163.83333333334</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>42500302</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="A6" t="str">
+        <v>2026-05-21 20:00:00</v>
+      </c>
+      <c r="B6" t="str">
+        <v>New York Knicks</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Cleveland Cavaliers</v>
+      </c>
+      <c r="D6" t="str">
+        <v>New York Knicks</v>
+      </c>
+      <c r="E6" t="str">
+        <v>0.9243</v>
+      </c>
+      <c r="F6" t="str">
+        <v>42500302</v>
+      </c>
+      <c r="G6" t="str">
+        <v>New York Knicks</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2026-05-22 20:30:00</v>
+      </c>
+      <c r="B7" t="str">
+        <v>San Antonio Spurs</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Oklahoma City Thunder</v>
+      </c>
+      <c r="D7" t="str">
+        <v>San Antonio Spurs</v>
+      </c>
+      <c r="E7" t="str">
+        <v>0.542427659</v>
+      </c>
+      <c r="F7" t="str">
+        <v>42500313</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -1,54 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="3">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -66,14 +49,82 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -152,7 +203,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -187,7 +237,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -222,16 +271,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -353,239 +406,659 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Date</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Home Team</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Away Team</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Predicted Winner</v>
-      </c>
-      <c r="E1" t="str">
-        <v>probability_home_win</v>
-      </c>
-      <c r="F1" t="str">
-        <v>gameId</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Actual Winner</v>
-      </c>
-      <c r="H1" t="str">
-        <v>market_prob_home_win</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Home Team</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Away Team</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Predicted Winner</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>probability_home_win</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>gameId</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Actual Winner</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>market_prob_home_win</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>2026-05-17 20:00:00</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Detroit Pistons</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Cleveland Cavaliers</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Detroit Pistons</v>
-      </c>
-      <c r="E2" t="str">
-        <v>0.6376</v>
-      </c>
-      <c r="F2" t="str">
-        <v>42500207</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Cleveland Cavaliers</v>
-      </c>
-      <c r="H2" t="str">
+      <c r="A2" s="1" t="n">
+        <v>46159.83333333334</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.6375999999999999</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>42500207</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>0.6279</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>2026-05-18 20:30:00</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Oklahoma City Thunder</v>
-      </c>
-      <c r="C3" t="str">
-        <v>San Antonio Spurs</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Oklahoma City Thunder</v>
-      </c>
-      <c r="E3" t="str">
+      <c r="A3" s="1" t="n">
+        <v>46160.85416666666</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>0.8002</v>
       </c>
-      <c r="F3" t="str">
-        <v>42500311</v>
-      </c>
-      <c r="G3" t="str">
-        <v>San Antonio Spurs</v>
-      </c>
-      <c r="H3" t="str">
-        <v>0.6779</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>42500311</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6778999999999999</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>2026-05-19 20:00:00</v>
-      </c>
-      <c r="B4" t="str">
-        <v>New York Knicks</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Cleveland Cavaliers</v>
-      </c>
-      <c r="D4" t="str">
-        <v>New York Knicks</v>
-      </c>
-      <c r="E4" t="str">
+      <c r="A4" s="1" t="n">
+        <v>46161.83333333334</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>0.837</v>
       </c>
-      <c r="F4" t="str">
-        <v>42500301</v>
-      </c>
-      <c r="G4" t="str">
-        <v>New York Knicks</v>
-      </c>
-      <c r="H4" t="str">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>42500301</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>0.6841</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>2026-05-20 20:30:00</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Oklahoma City Thunder</v>
-      </c>
-      <c r="C5" t="str">
-        <v>San Antonio Spurs</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Oklahoma City Thunder</v>
-      </c>
-      <c r="E5" t="str">
+      <c r="A5" s="1" t="n">
+        <v>46162.85416666666</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>0.662393162</v>
       </c>
-      <c r="F5" t="str">
-        <v>42500312</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Oklahoma City Thunder</v>
-      </c>
-      <c r="H5" t="str">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>42500312</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>0.6843</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>2026-05-21 20:00:00</v>
-      </c>
-      <c r="B6" t="str">
-        <v>New York Knicks</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Cleveland Cavaliers</v>
-      </c>
-      <c r="D6" t="str">
-        <v>New York Knicks</v>
-      </c>
-      <c r="E6" t="str">
+      <c r="A6" s="1" t="n">
+        <v>46163.83333333334</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>0.9243</v>
       </c>
-      <c r="F6" t="str">
-        <v>42500302</v>
-      </c>
-      <c r="G6" t="str">
-        <v>New York Knicks</v>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>42500302</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>2026-05-22 20:30:00</v>
-      </c>
-      <c r="B7" t="str">
-        <v>San Antonio Spurs</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Oklahoma City Thunder</v>
-      </c>
-      <c r="D7" t="str">
-        <v>San Antonio Spurs</v>
-      </c>
-      <c r="E7" t="str">
-        <v>0.542427659</v>
-      </c>
-      <c r="F7" t="str">
-        <v>42500313</v>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
+      <c r="A7" s="1" t="n">
+        <v>46164.85416666666</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.542427659034729</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>42500313</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.538</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46165.83333333334</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.4145455956459045</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>42500303</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5467</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46166.83333333334</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.5986899733543396</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>42500314</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5595</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46167.83333333334</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3377618193626404</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>42500304</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4473</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46168.85416666666</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.505280077457428</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>42500315</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6219</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46170.85416666666</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.6058698892593384</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>42500316</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46172.83333333334</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.6092059016227722</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>42500317</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46176.85416666666</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5307161808013916</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>42500401</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46178.85416666666</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7126911282539368</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>42500402</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6444</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46181.85416666666</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7088958024978638</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>42500403</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46183.85416666666</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8088039755821228</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>42500404</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5456</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46186.85416666666</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.5671389102935791</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>42500405</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>